--- a/artfynd/A 37532-2025 artfynd.xlsx
+++ b/artfynd/A 37532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127775019</v>
       </c>
       <c r="B2" t="n">
-        <v>96575</v>
+        <v>96581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37532-2025 artfynd.xlsx
+++ b/artfynd/A 37532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127775019</v>
       </c>
       <c r="B2" t="n">
-        <v>96581</v>
+        <v>96584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37532-2025 artfynd.xlsx
+++ b/artfynd/A 37532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127775019</v>
       </c>
       <c r="B2" t="n">
-        <v>96584</v>
+        <v>96592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37532-2025 artfynd.xlsx
+++ b/artfynd/A 37532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127775019</v>
       </c>
       <c r="B2" t="n">
-        <v>96592</v>
+        <v>96593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37532-2025 artfynd.xlsx
+++ b/artfynd/A 37532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127775019</v>
       </c>
       <c r="B2" t="n">
-        <v>96593</v>
+        <v>96594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37532-2025 artfynd.xlsx
+++ b/artfynd/A 37532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127775019</v>
       </c>
       <c r="B2" t="n">
-        <v>96594</v>
+        <v>96595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37532-2025 artfynd.xlsx
+++ b/artfynd/A 37532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127775019</v>
       </c>
       <c r="B2" t="n">
-        <v>96595</v>
+        <v>96603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37532-2025 artfynd.xlsx
+++ b/artfynd/A 37532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127775019</v>
       </c>
       <c r="B2" t="n">
-        <v>96603</v>
+        <v>96696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37532-2025 artfynd.xlsx
+++ b/artfynd/A 37532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127775019</v>
+        <v>127775010</v>
       </c>
       <c r="B2" t="n">
-        <v>96696</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781712</v>
+        <v>781742</v>
       </c>
       <c r="R2" t="n">
-        <v>7295584</v>
+        <v>7295599</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,6 +769,491 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127775006</v>
+      </c>
+      <c r="B3" t="n">
+        <v>95962</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2387</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pseudobryum cinclidioides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Maran/Täxtberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>781738</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7295573</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127775019</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97231</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Maran/Täxtberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>781712</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7295584</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127775020</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97231</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Maran/Täxtberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>781741</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7295574</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127774996</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Maran/Täxtberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>781676</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7295602</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127775002</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Maran/Täxtberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>781744</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7295597</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
